--- a/DQOPS_Package_20260212/DQOps_220_Pages_noVerticalMenu.xlsx
+++ b/DQOPS_Package_20260212/DQOps_220_Pages_noVerticalMenu.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ElisabetRovira\Downloads\DQOPS_Package_20260212\DQOPS_Package_20260212\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GKALWANI\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9EC4F7CC-DC90-4672-8FDD-B707ABE1C12E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F59974D-9E24-47C7-A04B-49A2147551D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43080" yWindow="12780" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pages" sheetId="2" r:id="rId1"/>
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6856" uniqueCount="1095">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6873" uniqueCount="1098">
   <si>
     <t>PageID</t>
   </si>
@@ -3410,6 +3410,15 @@
   </si>
   <si>
     <t>LocaleID</t>
+  </si>
+  <si>
+    <t>4b285cf2-6fcf-48bf-bd03-5f14821e6016</t>
+  </si>
+  <si>
+    <t>Users</t>
+  </si>
+  <si>
+    <t>webJSON_USERS_Hor</t>
   </si>
 </sst>
 </file>
@@ -3836,7 +3845,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61BC0BAB-5F26-4E0D-A53C-4AE7CA36B908}">
-  <dimension ref="A1:IV45"/>
+  <dimension ref="A1:IV46"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.1796875" style="2" customWidth="1"/>
@@ -3845,7 +3854,7 @@
     <col min="4" max="5" width="9.1796875" style="5"/>
     <col min="6" max="7" width="9.1796875" style="4"/>
     <col min="8" max="8" width="9.1796875" style="5"/>
-    <col min="9" max="9" width="17.81640625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="22.453125" style="5" customWidth="1"/>
     <col min="10" max="46" width="9.1796875" style="5"/>
     <col min="47" max="256" width="9.1796875" style="1"/>
   </cols>
@@ -10036,6 +10045,59 @@
         <v>1052</v>
       </c>
       <c r="AT45" s="5" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="46" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>1097</v>
+      </c>
+      <c r="N46" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="O46" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q46" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="R46" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="S46" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="U46" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="AP46" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="AT46" s="5" t="s">
         <v>1049</v>
       </c>
     </row>
@@ -25134,4 +25196,10 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{e760c494-6550-44b4-8258-77c175d778b7}" enabled="1" method="Privileged" siteId="{76a2ae5a-9f00-4f6b-95ed-5d33d77c4d61}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>